--- a/daily_matches/job_matches_2026-07-03.xlsx
+++ b/daily_matches/job_matches_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer (Data Scientist)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, PyTorch, FastAPI, Docker, Kubernetes</t>
+          <t>Data Scientist, RAG, Glue, Redshift, BigQuery, Synapse, Data Lake, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9330b23d69fd5c</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3d22f079d54bf0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cascade Financial Services</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>26.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Jenkins, Terraform, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, BigQuery, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=240acfcdaa55eae4</t>
+          <t>https://www.indeed.com/viewjob?jk=38b39caa4351d1c5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Managing Engineer - Risk Insights and Risk Engineering (Remote, US)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>QUARTERMASTER</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, S3, Glue, Redshift, Kinesis, CI/CD, Redshift, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfcda73cc0a3e91</t>
+          <t>https://www.indeed.com/viewjob?jk=926718992d1fd024</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pear Commerce</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Hadoop, MongoDB, Cassandra, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,1407 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7ead0889509d32</t>
+          <t>https://www.indeed.com/viewjob?jk=d7dce5ca3032b2ad</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Senior Software Engineer - Python/Agentic AI - EU Remote</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AllStars-IT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, Copilot, Kubernetes, CI/CD, Terraform, PostgreSQL, MongoDB, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a091b79f52b8cba</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>American Civil Liberties Union</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fef81ca1522be027</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Everforth ECS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Databricks, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f4b7618c4e8b759</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Databricks AI Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Hugging Face, FAISS, Pinecone, MLflow, CI/CD, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a804052bd134768</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Logisnext Americas Inc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Snowflake, Databricks, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9442e33d8fc54bc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Data Architect and Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Logisnext Americas Inc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Snowflake, Databricks, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3c56a8e57b8b032</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Senior AI Engineer</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Menlo Park, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Chemours</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, PyTorch, Kubernetes, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40758ce122074d1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sr Forward Deployed Engineer - AI Enablement</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The Trade Desk</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bbb15c1ffe3ebb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sr Forward Deployed Engineer - AI Enablement</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The Trade Desk</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad5bd5d06190f943</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sr Forward Deployed Engineer - AI Enablement</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>The Trade Desk</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb75ea461f967543</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sr Forward Deployed Engineer - AI Enablement</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The Trade Desk</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6389b756726bffe</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Teradata</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Kubernetes, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9f1a97173570192</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Teradata</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Kubernetes, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8aa58f7723b9f05b</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Big Data / AWS Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Jenkins, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85e1e53cf29b5e7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Goodship</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d03553580734b186</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>REAL Broker, LLC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e07bfb2d72095e74</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>REAL Broker, LLC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53bfd7b5833400cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>REAL Broker, LLC</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de2adbc459556c0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>REAL Broker, LLC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c19997f0c6442189</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>REAL Broker, LLC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=823b104e0c37ebcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>REAL Broker, LLC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a227e8b621a043e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>REAL Broker, LLC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c204627afe28e82</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>REAL Broker, LLC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ececa7e98a494d42</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>REAL Broker, LLC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d746558687544e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>REAL Broker, LLC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3f7b5fb2120052f</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>REAL Broker, LLC</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f36fbc1e9cce240</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>REAL Broker, LLC</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Newark, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53365d0170096079</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>REAL Broker, LLC</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de0969a6cccae978</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>REAL Broker, LLC</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76a0bf826df93ae4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>REAL Broker, LLC</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e0fa4832f3cd6b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AI Operations Intern</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Frontline Education</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, Copilot, Cortex, Snowflake, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2869709283c49a</t>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, PostgreSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a59780ca08cbf32</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend, Level 5</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77a82cf11250ddc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>General Dynamics Information Technology</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Chantilly, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac3d72a08dea6d97</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>General Dynamics Information Technology</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Chantilly, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38deea2dac8d4ff8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, CI/CD, Databricks, PySpark, SQL, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fac7de54c53bfc14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Gordon Food Service</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Wyoming, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Gemini, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=396b81875d0a878c</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Gordon Food Service</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Gemini, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d0dd5d4fad40481</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Consultant, SIEM Engineer (Logstash)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Infinitive Inc</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ee32c9f434de08a</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BMS Data Analysis Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>microvast</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Tableau, Power BI, Matplotlib, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9118e7f9e8e28e1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Altamira Technologies Corp.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Fairborn, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Keras, Docker, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=963cdd0c9d1e97fc</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-03.xlsx
+++ b/daily_matches/job_matches_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Obsidian Security</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Snowflake, Databricks, Kafka, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, TensorFlow, PyTorch, AWS SageMaker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3534616cc26c3b28</t>
+          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Development Engineer (AI Engineering)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Obsidian Security</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Snowflake, Databricks, Kafka, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,129 +531,129 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c9d982ae2aa8c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=66d09b0b6d5ce470</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DBT Developer</t>
+          <t>Full Stack Java Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OSI Digital</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Tableau, Python, SQL, R</t>
+          <t>RAG, Copilot, YOLO, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8765bd1c65b5570</t>
+          <t>https://www.indeed.com/viewjob?jk=663a240a6b6579e6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java Microservices</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Berwyn, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Jenkins, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>Generative AI, RAG, Hugging Face, Prompt Engineering, S3, Docker, Kafka, Hadoop, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e61132fea688dd</t>
+          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineering - Generative AI &amp; Agentic AI</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Colgate University</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Middletown, NJ, US USA</t>
+          <t>Hamilton, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+          <t>LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Redshift, Kubernetes, Terraform, Git, Redshift</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5af1e0aafe001ad</t>
+          <t>https://www.indeed.com/viewjob?jk=56223bbd023f84d5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineering - Generative AI &amp; Agentic AI</t>
+          <t>Software Engineer III - J2EE/Spring Boot</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+          <t>RAG, S3, Kubernetes, Git, Kafka, Cassandra, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a384ea079faa3d</t>
+          <t>https://www.indeed.com/viewjob?jk=c4275ed2bedf6106</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineering - Generative AI &amp; Agentic AI</t>
+          <t>Computer Vision Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, Keras, OpenCV, MySQL, Matplotlib, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,147 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0289e1c67f689348</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcbcaaa7d8189f8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Waterloo, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81913d589c038b43</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Analyst / Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>McAfee</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Kafka, PostgreSQL, MongoDB, NoSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7243895dcaddd8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer IV</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>University of Louisville</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=206097d80ffbaf49</t>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6939d33deccd362</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-03.xlsx
+++ b/daily_matches/job_matches_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Asset &amp; Wealth Management - Software Engineer, AI Platform and Services - Associate - Richardson</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, TensorFlow, PyTorch, AWS SageMaker</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, LLaMA, Gemini, Prompt Engineering, S3, Redshift, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bb6b860bdff8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3c31523160462d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer (AI Engineering)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>S3, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66d09b0b6d5ce470</t>
+          <t>https://www.indeed.com/viewjob?jk=23c4fce757383114</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Java Engineer</t>
+          <t>Software Engineer II - Python</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, YOLO, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL</t>
+          <t>Copilot, EC2, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,102 +566,102 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663a240a6b6579e6</t>
+          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>AllStars-IT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, Prompt Engineering, S3, Docker, Kafka, Hadoop, MongoDB, Cassandra</t>
+          <t>Data Scientist, Generative AI, RAG, Kafka, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ff02de6ff660e7</t>
+          <t>https://www.indeed.com/viewjob?jk=74da2d187b8f8454</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Colgate University</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hamilton, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Redshift, Kubernetes, Terraform, Git, Redshift</t>
+          <t>RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56223bbd023f84d5</t>
+          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III - J2EE/Spring Boot</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, Git, Kafka, Cassandra, NoSQL, SQL, R, Java</t>
+          <t>Generative AI, RAG, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,182 +671,42 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4275ed2bedf6106</t>
+          <t>https://www.indeed.com/viewjob?jk=d3da4bd93b7aa38f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Computer Vision Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, Keras, OpenCV, MySQL, Matplotlib, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcbcaaa7d8189f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Genpact</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81913d589c038b43</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Data Analyst / Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>McAfee</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Kafka, PostgreSQL, MongoDB, NoSQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24abff5e97729f1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b7243895dcaddd8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Business Intelligence Engineer IV</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>University of Louisville</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d6939d33deccd362</t>
+          <t>https://www.indeed.com/viewjob?jk=59f3738ac41acdda</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-03.xlsx
+++ b/daily_matches/job_matches_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer, AI Platform and Services - Associate - Richardson</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Awesome Motive Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Miami Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, LLaMA, Gemini, Prompt Engineering, S3, Redshift, Terraform, Git</t>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, ChromaDB, AWS SageMaker, MLflow, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3c31523160462d</t>
+          <t>https://www.indeed.com/viewjob?jk=98f33599b59c5df8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer 2 ( React and Python)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S3, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23c4fce757383114</t>
+          <t>https://www.indeed.com/viewjob?jk=38748aa3ba6711fa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python</t>
+          <t>Software Engineer 2 ( React and Python)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Copilot, EC2, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb780f85c387dcda</t>
+          <t>https://www.indeed.com/viewjob?jk=4262c294fe7dd22b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Java Golang Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AllStars-IT</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kafka, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74da2d187b8f8454</t>
+          <t>https://www.indeed.com/viewjob?jk=52b5df568a77d80f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Campus DTAI Track – Data, Tech &amp; AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Hudson River Community Credit Union</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Corinth, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Glue, Git, Snowflake, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6629e5da1fcb9599</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7fcbb496808adb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Automations &amp; AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,15 +653,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, Prompt Engineering, Docker, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,77 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3da4bd93b7aa38f</t>
+          <t>https://www.indeed.com/viewjob?jk=b58b08d5ae33fc94</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Altak Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, AWS SageMaker, Glue, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=014f5c343e0570a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI Operations Intern</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Frontline Education</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, PostgreSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=59f3738ac41acdda</t>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72511f893299c8d1</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-03.xlsx
+++ b/daily_matches/job_matches_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Senior Data Scientist – GenAI, LLM &amp; RAG | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Awesome Motive Inc.</t>
+          <t>Tricon Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Miami Beach, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, ChromaDB, AWS SageMaker, MLflow, FastAPI, Docker</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Git, Snowflake, Hadoop, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f33599b59c5df8</t>
+          <t>https://www.indeed.com/viewjob?jk=8004f011ac10dbac</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( React and Python)</t>
+          <t>Customer Delivery Architect(Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, Power BI, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38748aa3ba6711fa</t>
+          <t>https://www.indeed.com/viewjob?jk=59c791c401a7daac</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( React and Python)</t>
+          <t>Customer Delivery Architect (Remote)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, Power BI, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,182 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4262c294fe7dd22b</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Java Golang Developer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52b5df568a77d80f</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Hudson River Community Credit Union</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Corinth, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Glue, Git, Snowflake, Databricks, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7fcbb496808adb</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Automations &amp; AI Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Prompt Engineering, Docker, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b58b08d5ae33fc94</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Altak Group</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, AWS SageMaker, Glue, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=014f5c343e0570a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AI Operations Intern</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Frontline Education</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, PostgreSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72511f893299c8d1</t>
+          <t>https://www.indeed.com/viewjob?jk=3c5342afa2c5f2a0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-03.xlsx
+++ b/daily_matches/job_matches_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – GenAI, LLM &amp; RAG | Oil &amp; Gas Domain | Houston, TX | Full-Time</t>
+          <t>Software Engineer (Level 3 / E3) - Core Platform</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tricon Solutions</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Git, Snowflake, Hadoop, Tableau, Power BI</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, MongoDB, Cassandra, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8004f011ac10dbac</t>
+          <t>https://www.indeed.com/viewjob?jk=4e46ba444bbad5fd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Customer Delivery Architect(Remote)</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>CADRE GOVERNMENT SOLUTIONS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,112 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59c791c401a7daac</t>
+          <t>https://www.indeed.com/viewjob?jk=e2099b5430245346</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Customer Delivery Architect (Remote)</t>
+          <t>Software Engineer (Level 4 / E4) - Core Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, MongoDB, Cassandra, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ffad5f6aac08e5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Junior AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Snowflake, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b53e41bd1322624</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Snowflake, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c5342afa2c5f2a0</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc379557ac7b50a7</t>
         </is>
       </c>
     </row>
